--- a/public/alpensia_template.xlsx
+++ b/public/alpensia_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\초이스골프(공유폴더)\26년도 알펜시아\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{615FA8B5-3C77-44B0-A0FE-10D2631F30D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DCEBE16-9AAC-4B8C-B4B2-DA406CABFC57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1702,6 +1702,201 @@
     <xf numFmtId="0" fontId="27" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="15" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="15" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="3" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="3" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="3" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="3" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="3" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="3" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="3" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="19" fillId="3" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="19" fillId="3" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="3" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1714,18 +1909,6 @@
     <xf numFmtId="41" fontId="5" fillId="3" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="177" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1735,18 +1918,9 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="41" fontId="0" fillId="3" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1778,180 +1952,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="19" fillId="3" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="19" fillId="3" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="3" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="3" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="3" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="3" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="3" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="3" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="3" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="3" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="15" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="15" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2327,31 +2327,31 @@
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="72" t="s">
+      <c r="E1" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
       <c r="L1" s="38"/>
     </row>
     <row r="2" spans="1:12" s="5" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="144" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="86"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
-      <c r="H2" s="86"/>
-      <c r="I2" s="86"/>
-      <c r="J2" s="86"/>
-      <c r="K2" s="86"/>
+      <c r="B2" s="144"/>
+      <c r="C2" s="144"/>
+      <c r="D2" s="144"/>
+      <c r="E2" s="144"/>
+      <c r="F2" s="144"/>
+      <c r="G2" s="144"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="144"/>
       <c r="L2" s="22"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -2364,12 +2364,12 @@
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="90" t="s">
+      <c r="B5" s="148" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="90"/>
-      <c r="D5" s="90"/>
-      <c r="E5" s="90"/>
+      <c r="C5" s="148"/>
+      <c r="D5" s="148"/>
+      <c r="E5" s="148"/>
       <c r="F5" s="25" t="s">
         <v>4</v>
       </c>
@@ -2394,44 +2394,44 @@
       <c r="A6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="91" t="s">
+      <c r="B6" s="149" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="91"/>
-      <c r="D6" s="91"/>
-      <c r="E6" s="91"/>
+      <c r="C6" s="149"/>
+      <c r="D6" s="149"/>
+      <c r="E6" s="149"/>
       <c r="F6" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="87" t="s">
+      <c r="G6" s="145" t="s">
         <v>63</v>
       </c>
-      <c r="H6" s="88"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="88"/>
-      <c r="K6" s="89"/>
+      <c r="H6" s="146"/>
+      <c r="I6" s="146"/>
+      <c r="J6" s="146"/>
+      <c r="K6" s="147"/>
       <c r="L6" s="7"/>
     </row>
     <row r="7" spans="1:12" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="93" t="s">
+      <c r="B7" s="151" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="93"/>
-      <c r="D7" s="93"/>
-      <c r="E7" s="93"/>
+      <c r="C7" s="151"/>
+      <c r="D7" s="151"/>
+      <c r="E7" s="151"/>
       <c r="F7" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="94" t="s">
+      <c r="G7" s="152" t="s">
         <v>65</v>
       </c>
-      <c r="H7" s="95"/>
-      <c r="I7" s="95"/>
-      <c r="J7" s="95"/>
-      <c r="K7" s="96"/>
+      <c r="H7" s="153"/>
+      <c r="I7" s="153"/>
+      <c r="J7" s="153"/>
+      <c r="K7" s="154"/>
       <c r="L7" s="26"/>
     </row>
     <row r="8" spans="1:12" ht="3.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2449,19 +2449,19 @@
       <c r="L8" s="7"/>
     </row>
     <row r="9" spans="1:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="92" t="s">
+      <c r="A9" s="150" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="92"/>
-      <c r="C9" s="92"/>
-      <c r="D9" s="92"/>
-      <c r="E9" s="92"/>
-      <c r="F9" s="92"/>
-      <c r="G9" s="92"/>
-      <c r="H9" s="92"/>
-      <c r="I9" s="92"/>
-      <c r="J9" s="92"/>
-      <c r="K9" s="92"/>
+      <c r="B9" s="150"/>
+      <c r="C9" s="150"/>
+      <c r="D9" s="150"/>
+      <c r="E9" s="150"/>
+      <c r="F9" s="150"/>
+      <c r="G9" s="150"/>
+      <c r="H9" s="150"/>
+      <c r="I9" s="150"/>
+      <c r="J9" s="150"/>
+      <c r="K9" s="150"/>
       <c r="L9" s="26"/>
     </row>
     <row r="10" spans="1:12" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
@@ -2486,10 +2486,10 @@
       <c r="G10" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="97" t="s">
+      <c r="H10" s="111" t="s">
         <v>49</v>
       </c>
-      <c r="I10" s="98"/>
+      <c r="I10" s="112"/>
       <c r="J10" s="70" t="s">
         <v>48</v>
       </c>
@@ -2514,14 +2514,14 @@
       <c r="E11" s="18">
         <v>4</v>
       </c>
-      <c r="F11" s="153">
+      <c r="F11" s="71">
         <v>0.49791666666666662</v>
       </c>
       <c r="G11" s="10"/>
-      <c r="H11" s="82">
+      <c r="H11" s="113">
         <v>140000</v>
       </c>
-      <c r="I11" s="99"/>
+      <c r="I11" s="107"/>
       <c r="J11" s="45"/>
       <c r="K11" s="51">
         <f>SUM(((D11*4)*H11)+(E11*J11))</f>
@@ -2545,14 +2545,14 @@
       <c r="E12" s="18">
         <v>4</v>
       </c>
-      <c r="F12" s="154">
+      <c r="F12" s="72">
         <v>0.45902777777777781</v>
       </c>
       <c r="G12" s="11"/>
-      <c r="H12" s="115">
+      <c r="H12" s="131">
         <v>120000</v>
       </c>
-      <c r="I12" s="116"/>
+      <c r="I12" s="110"/>
       <c r="J12" s="44"/>
       <c r="K12" s="51">
         <f t="shared" ref="K12:K13" si="0">SUM(((D12*4)*H12)+(E12*J12))</f>
@@ -2568,8 +2568,8 @@
       <c r="E13" s="23"/>
       <c r="F13" s="28"/>
       <c r="G13" s="11"/>
-      <c r="H13" s="115"/>
-      <c r="I13" s="116"/>
+      <c r="H13" s="131"/>
+      <c r="I13" s="110"/>
       <c r="J13" s="44"/>
       <c r="K13" s="51">
         <f t="shared" si="0"/>
@@ -2585,8 +2585,8 @@
       <c r="E14" s="14"/>
       <c r="F14" s="39"/>
       <c r="G14" s="12"/>
-      <c r="H14" s="111"/>
-      <c r="I14" s="112"/>
+      <c r="H14" s="128"/>
+      <c r="I14" s="95"/>
       <c r="J14" s="46"/>
       <c r="K14" s="51">
         <f>SUM(((D14*4)*H14)+(E14*J14))</f>
@@ -2595,38 +2595,38 @@
       <c r="L14" s="31"/>
     </row>
     <row r="15" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="75" t="s">
+      <c r="A15" s="115" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="76"/>
-      <c r="C15" s="76"/>
-      <c r="D15" s="76"/>
-      <c r="E15" s="76"/>
-      <c r="F15" s="76"/>
-      <c r="G15" s="76"/>
-      <c r="H15" s="76"/>
-      <c r="I15" s="77"/>
-      <c r="J15" s="73">
+      <c r="B15" s="116"/>
+      <c r="C15" s="116"/>
+      <c r="D15" s="116"/>
+      <c r="E15" s="116"/>
+      <c r="F15" s="116"/>
+      <c r="G15" s="116"/>
+      <c r="H15" s="116"/>
+      <c r="I15" s="117"/>
+      <c r="J15" s="138">
         <f>SUM(K11:K14)</f>
         <v>1040000</v>
       </c>
-      <c r="K15" s="74"/>
+      <c r="K15" s="139"/>
       <c r="L15" s="32"/>
     </row>
     <row r="16" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="121" t="s">
+      <c r="A16" s="97" t="s">
         <v>59</v>
       </c>
-      <c r="B16" s="121"/>
-      <c r="C16" s="121"/>
-      <c r="D16" s="121"/>
-      <c r="E16" s="121"/>
-      <c r="F16" s="121"/>
-      <c r="G16" s="121"/>
-      <c r="H16" s="121"/>
-      <c r="I16" s="121"/>
-      <c r="J16" s="121"/>
-      <c r="K16" s="121"/>
+      <c r="B16" s="97"/>
+      <c r="C16" s="97"/>
+      <c r="D16" s="97"/>
+      <c r="E16" s="97"/>
+      <c r="F16" s="97"/>
+      <c r="G16" s="97"/>
+      <c r="H16" s="97"/>
+      <c r="I16" s="97"/>
+      <c r="J16" s="97"/>
+      <c r="K16" s="97"/>
       <c r="L16" s="33"/>
     </row>
     <row r="17" spans="1:12" ht="3.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2644,19 +2644,19 @@
       <c r="L17" s="17"/>
     </row>
     <row r="18" spans="1:12" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="100" t="s">
+      <c r="A18" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="100"/>
-      <c r="C18" s="100"/>
-      <c r="D18" s="100"/>
-      <c r="E18" s="100"/>
-      <c r="F18" s="100"/>
-      <c r="G18" s="100"/>
-      <c r="H18" s="100"/>
-      <c r="I18" s="100"/>
-      <c r="J18" s="100"/>
-      <c r="K18" s="100"/>
+      <c r="B18" s="114"/>
+      <c r="C18" s="114"/>
+      <c r="D18" s="114"/>
+      <c r="E18" s="114"/>
+      <c r="F18" s="114"/>
+      <c r="G18" s="114"/>
+      <c r="H18" s="114"/>
+      <c r="I18" s="114"/>
+      <c r="J18" s="114"/>
+      <c r="K18" s="114"/>
       <c r="L18" s="26"/>
     </row>
     <row r="19" spans="1:12" s="9" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2669,22 +2669,22 @@
       <c r="C19" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="122" t="s">
+      <c r="D19" s="98" t="s">
         <v>16</v>
       </c>
-      <c r="E19" s="123"/>
+      <c r="E19" s="99"/>
       <c r="F19" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G19" s="124" t="s">
+      <c r="G19" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="H19" s="125"/>
-      <c r="I19" s="126"/>
-      <c r="J19" s="80" t="s">
+      <c r="H19" s="103"/>
+      <c r="I19" s="104"/>
+      <c r="J19" s="141" t="s">
         <v>14</v>
       </c>
-      <c r="K19" s="81"/>
+      <c r="K19" s="142"/>
       <c r="L19" s="34"/>
     </row>
     <row r="20" spans="1:12" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
@@ -2697,92 +2697,92 @@
       <c r="C20" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="113" t="s">
+      <c r="D20" s="129" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="114"/>
+      <c r="E20" s="130"/>
       <c r="F20" s="19">
         <v>2</v>
       </c>
-      <c r="G20" s="127">
+      <c r="G20" s="105">
         <v>150000</v>
       </c>
-      <c r="H20" s="128"/>
-      <c r="I20" s="99"/>
-      <c r="J20" s="82">
+      <c r="H20" s="106"/>
+      <c r="I20" s="107"/>
+      <c r="J20" s="113">
         <f>SUM(F20*G20)</f>
         <v>300000</v>
       </c>
-      <c r="K20" s="83"/>
+      <c r="K20" s="143"/>
       <c r="L20" s="35"/>
     </row>
     <row r="21" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="40"/>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
-      <c r="D21" s="119"/>
-      <c r="E21" s="120"/>
+      <c r="D21" s="134"/>
+      <c r="E21" s="135"/>
       <c r="F21" s="19"/>
-      <c r="G21" s="129"/>
-      <c r="H21" s="130"/>
-      <c r="I21" s="116"/>
-      <c r="J21" s="84">
+      <c r="G21" s="108"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="110"/>
+      <c r="J21" s="100">
         <f>SUM(F21*G21)</f>
         <v>0</v>
       </c>
-      <c r="K21" s="85"/>
+      <c r="K21" s="101"/>
       <c r="L21" s="35"/>
     </row>
     <row r="22" spans="1:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="41"/>
       <c r="B22" s="23"/>
       <c r="C22" s="23"/>
-      <c r="D22" s="117"/>
-      <c r="E22" s="118"/>
+      <c r="D22" s="132"/>
+      <c r="E22" s="133"/>
       <c r="F22" s="24"/>
-      <c r="G22" s="131"/>
-      <c r="H22" s="132"/>
-      <c r="I22" s="112"/>
-      <c r="J22" s="84">
+      <c r="G22" s="93"/>
+      <c r="H22" s="94"/>
+      <c r="I22" s="95"/>
+      <c r="J22" s="100">
         <f>SUM(F22*G22)</f>
         <v>0</v>
       </c>
-      <c r="K22" s="85"/>
+      <c r="K22" s="101"/>
       <c r="L22" s="35"/>
     </row>
     <row r="23" spans="1:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="75" t="s">
+      <c r="A23" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="76"/>
-      <c r="C23" s="76"/>
-      <c r="D23" s="76"/>
-      <c r="E23" s="76"/>
-      <c r="F23" s="76"/>
-      <c r="G23" s="76"/>
-      <c r="H23" s="76"/>
-      <c r="I23" s="77"/>
-      <c r="J23" s="101">
+      <c r="B23" s="116"/>
+      <c r="C23" s="116"/>
+      <c r="D23" s="116"/>
+      <c r="E23" s="116"/>
+      <c r="F23" s="116"/>
+      <c r="G23" s="116"/>
+      <c r="H23" s="116"/>
+      <c r="I23" s="117"/>
+      <c r="J23" s="118">
         <f>SUM(J20:K22)</f>
         <v>300000</v>
       </c>
-      <c r="K23" s="102"/>
+      <c r="K23" s="119"/>
       <c r="L23" s="36"/>
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="103" t="s">
+      <c r="A24" s="120" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="103"/>
-      <c r="C24" s="103"/>
-      <c r="D24" s="103"/>
-      <c r="E24" s="103"/>
-      <c r="F24" s="103"/>
-      <c r="G24" s="103"/>
-      <c r="H24" s="103"/>
-      <c r="I24" s="103"/>
-      <c r="J24" s="103"/>
-      <c r="K24" s="103"/>
+      <c r="B24" s="120"/>
+      <c r="C24" s="120"/>
+      <c r="D24" s="120"/>
+      <c r="E24" s="120"/>
+      <c r="F24" s="120"/>
+      <c r="G24" s="120"/>
+      <c r="H24" s="120"/>
+      <c r="I24" s="120"/>
+      <c r="J24" s="120"/>
+      <c r="K24" s="120"/>
       <c r="L24" s="36"/>
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2802,187 +2802,187 @@
       <c r="L25" s="37"/>
     </row>
     <row r="26" spans="1:12" ht="22.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="106" t="s">
+      <c r="A26" s="123" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="107"/>
-      <c r="C26" s="107"/>
-      <c r="D26" s="107"/>
-      <c r="E26" s="107"/>
-      <c r="F26" s="107"/>
-      <c r="G26" s="107"/>
-      <c r="H26" s="107"/>
-      <c r="I26" s="108"/>
-      <c r="J26" s="104">
+      <c r="B26" s="124"/>
+      <c r="C26" s="124"/>
+      <c r="D26" s="124"/>
+      <c r="E26" s="124"/>
+      <c r="F26" s="124"/>
+      <c r="G26" s="124"/>
+      <c r="H26" s="124"/>
+      <c r="I26" s="125"/>
+      <c r="J26" s="121">
         <f>SUM(J15+J23)</f>
         <v>1340000</v>
       </c>
-      <c r="K26" s="105"/>
+      <c r="K26" s="122"/>
       <c r="L26" s="37"/>
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="109"/>
-      <c r="C27" s="109"/>
-      <c r="D27" s="109"/>
-      <c r="E27" s="109"/>
-      <c r="F27" s="109"/>
-      <c r="G27" s="109"/>
-      <c r="H27" s="109"/>
-      <c r="I27" s="109"/>
-      <c r="J27" s="109"/>
-      <c r="K27" s="110"/>
+      <c r="B27" s="126"/>
+      <c r="C27" s="126"/>
+      <c r="D27" s="126"/>
+      <c r="E27" s="126"/>
+      <c r="F27" s="126"/>
+      <c r="G27" s="126"/>
+      <c r="H27" s="126"/>
+      <c r="I27" s="126"/>
+      <c r="J27" s="126"/>
+      <c r="K27" s="127"/>
       <c r="L27" s="37"/>
     </row>
     <row r="28" spans="1:12" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="100" t="s">
+      <c r="A28" s="114" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="100"/>
-      <c r="C28" s="100"/>
-      <c r="D28" s="100"/>
-      <c r="E28" s="100"/>
-      <c r="F28" s="100"/>
-      <c r="G28" s="100"/>
-      <c r="H28" s="100"/>
-      <c r="I28" s="100"/>
-      <c r="J28" s="100"/>
-      <c r="K28" s="100"/>
+      <c r="B28" s="114"/>
+      <c r="C28" s="114"/>
+      <c r="D28" s="114"/>
+      <c r="E28" s="114"/>
+      <c r="F28" s="114"/>
+      <c r="G28" s="114"/>
+      <c r="H28" s="114"/>
+      <c r="I28" s="114"/>
+      <c r="J28" s="114"/>
+      <c r="K28" s="114"/>
       <c r="L28" s="26"/>
     </row>
     <row r="29" spans="1:12" s="68" customFormat="1" ht="13.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="152" t="s">
+      <c r="A29" s="92" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="133"/>
-      <c r="C29" s="133"/>
-      <c r="D29" s="133" t="s">
+      <c r="B29" s="76"/>
+      <c r="C29" s="76"/>
+      <c r="D29" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="E29" s="133"/>
-      <c r="F29" s="133"/>
-      <c r="G29" s="133"/>
-      <c r="H29" s="133" t="s">
+      <c r="E29" s="76"/>
+      <c r="F29" s="76"/>
+      <c r="G29" s="76"/>
+      <c r="H29" s="76" t="s">
         <v>43</v>
       </c>
-      <c r="I29" s="133"/>
-      <c r="J29" s="133"/>
-      <c r="K29" s="138"/>
+      <c r="I29" s="76"/>
+      <c r="J29" s="76"/>
+      <c r="K29" s="77"/>
       <c r="L29" s="66"/>
     </row>
     <row r="30" spans="1:12" s="68" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="146" t="s">
+      <c r="A30" s="86" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="147"/>
-      <c r="C30" s="147"/>
-      <c r="D30" s="134" t="s">
+      <c r="B30" s="87"/>
+      <c r="C30" s="87"/>
+      <c r="D30" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="E30" s="134"/>
-      <c r="F30" s="134"/>
-      <c r="G30" s="134"/>
-      <c r="H30" s="134" t="s">
+      <c r="E30" s="78"/>
+      <c r="F30" s="78"/>
+      <c r="G30" s="78"/>
+      <c r="H30" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="I30" s="134"/>
-      <c r="J30" s="134"/>
-      <c r="K30" s="139"/>
+      <c r="I30" s="78"/>
+      <c r="J30" s="78"/>
+      <c r="K30" s="79"/>
       <c r="L30" s="67"/>
     </row>
     <row r="31" spans="1:12" s="68" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="148" t="s">
+      <c r="A31" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="B31" s="149"/>
-      <c r="C31" s="149"/>
-      <c r="D31" s="78" t="s">
+      <c r="B31" s="89"/>
+      <c r="C31" s="89"/>
+      <c r="D31" s="96" t="s">
         <v>41</v>
       </c>
-      <c r="E31" s="78"/>
-      <c r="F31" s="78"/>
-      <c r="G31" s="78"/>
-      <c r="H31" s="78" t="s">
+      <c r="E31" s="96"/>
+      <c r="F31" s="96"/>
+      <c r="G31" s="96"/>
+      <c r="H31" s="96" t="s">
         <v>41</v>
       </c>
-      <c r="I31" s="78"/>
-      <c r="J31" s="78"/>
-      <c r="K31" s="79"/>
+      <c r="I31" s="96"/>
+      <c r="J31" s="96"/>
+      <c r="K31" s="140"/>
       <c r="L31" s="67"/>
     </row>
     <row r="32" spans="1:12" s="68" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="148" t="s">
+      <c r="A32" s="88" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="149"/>
-      <c r="C32" s="149"/>
-      <c r="D32" s="78" t="s">
+      <c r="B32" s="89"/>
+      <c r="C32" s="89"/>
+      <c r="D32" s="96" t="s">
         <v>42</v>
       </c>
-      <c r="E32" s="78"/>
-      <c r="F32" s="78"/>
-      <c r="G32" s="78"/>
-      <c r="H32" s="78" t="s">
+      <c r="E32" s="96"/>
+      <c r="F32" s="96"/>
+      <c r="G32" s="96"/>
+      <c r="H32" s="96" t="s">
         <v>44</v>
       </c>
-      <c r="I32" s="78"/>
-      <c r="J32" s="78"/>
-      <c r="K32" s="79"/>
+      <c r="I32" s="96"/>
+      <c r="J32" s="96"/>
+      <c r="K32" s="140"/>
       <c r="L32" s="67"/>
     </row>
     <row r="33" spans="1:12" s="68" customFormat="1" ht="13.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="150" t="s">
+      <c r="A33" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="151"/>
-      <c r="C33" s="151"/>
-      <c r="D33" s="135" t="s">
+      <c r="B33" s="91"/>
+      <c r="C33" s="91"/>
+      <c r="D33" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E33" s="136"/>
-      <c r="F33" s="136"/>
-      <c r="G33" s="136"/>
-      <c r="H33" s="136"/>
-      <c r="I33" s="136"/>
-      <c r="J33" s="136"/>
-      <c r="K33" s="137"/>
+      <c r="E33" s="74"/>
+      <c r="F33" s="74"/>
+      <c r="G33" s="74"/>
+      <c r="H33" s="74"/>
+      <c r="I33" s="74"/>
+      <c r="J33" s="74"/>
+      <c r="K33" s="75"/>
       <c r="L33" s="67"/>
     </row>
     <row r="34" spans="1:12" s="68" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="140" t="s">
+      <c r="A34" s="80" t="s">
         <v>53</v>
       </c>
-      <c r="B34" s="141"/>
-      <c r="C34" s="141"/>
-      <c r="D34" s="141"/>
-      <c r="E34" s="141"/>
-      <c r="F34" s="141"/>
-      <c r="G34" s="141"/>
-      <c r="H34" s="141"/>
-      <c r="I34" s="141"/>
-      <c r="J34" s="141"/>
-      <c r="K34" s="142"/>
+      <c r="B34" s="81"/>
+      <c r="C34" s="81"/>
+      <c r="D34" s="81"/>
+      <c r="E34" s="81"/>
+      <c r="F34" s="81"/>
+      <c r="G34" s="81"/>
+      <c r="H34" s="81"/>
+      <c r="I34" s="81"/>
+      <c r="J34" s="81"/>
+      <c r="K34" s="82"/>
       <c r="L34" s="67"/>
     </row>
     <row r="35" spans="1:12" s="68" customFormat="1" ht="13.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="143" t="s">
+      <c r="A35" s="83" t="s">
         <v>50</v>
       </c>
-      <c r="B35" s="144"/>
-      <c r="C35" s="144"/>
-      <c r="D35" s="144"/>
-      <c r="E35" s="144"/>
-      <c r="F35" s="144"/>
-      <c r="G35" s="144"/>
-      <c r="H35" s="144"/>
-      <c r="I35" s="144"/>
-      <c r="J35" s="144"/>
-      <c r="K35" s="145"/>
+      <c r="B35" s="84"/>
+      <c r="C35" s="84"/>
+      <c r="D35" s="84"/>
+      <c r="E35" s="84"/>
+      <c r="F35" s="84"/>
+      <c r="G35" s="84"/>
+      <c r="H35" s="84"/>
+      <c r="I35" s="84"/>
+      <c r="J35" s="84"/>
+      <c r="K35" s="85"/>
       <c r="L35" s="67"/>
     </row>
-    <row r="36" spans="1:12" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="52" t="s">
         <v>31</v>
       </c>
@@ -2998,7 +2998,7 @@
       <c r="K36" s="49"/>
       <c r="L36" s="13"/>
     </row>
-    <row r="37" spans="1:12" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="52" t="s">
         <v>56</v>
       </c>
@@ -3014,7 +3014,7 @@
       <c r="K37" s="49"/>
       <c r="L37" s="13"/>
     </row>
-    <row r="38" spans="1:12" s="13" customFormat="1" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" s="13" customFormat="1" ht="6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="52" t="s">
         <v>32</v>
       </c>
@@ -3029,7 +3029,7 @@
       <c r="J38" s="49"/>
       <c r="K38" s="49"/>
     </row>
-    <row r="39" spans="1:12" s="13" customFormat="1" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" s="13" customFormat="1" ht="6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="52" t="s">
         <v>33</v>
       </c>
@@ -3045,7 +3045,7 @@
       <c r="K39" s="50"/>
       <c r="L39"/>
     </row>
-    <row r="40" spans="1:12" s="13" customFormat="1" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" s="13" customFormat="1" ht="6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="52" t="s">
         <v>55</v>
       </c>
@@ -3060,7 +3060,7 @@
       <c r="J40" s="49"/>
       <c r="K40" s="49"/>
     </row>
-    <row r="41" spans="1:12" s="13" customFormat="1" ht="10.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" s="13" customFormat="1" ht="6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="48" t="s">
         <v>51</v>
       </c>
@@ -3075,7 +3075,7 @@
       <c r="J41" s="49"/>
       <c r="K41" s="49"/>
     </row>
-    <row r="42" spans="1:12" ht="10.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="48" t="s">
         <v>28</v>
       </c>
@@ -3090,7 +3090,7 @@
       <c r="J42" s="50"/>
       <c r="K42" s="50"/>
     </row>
-    <row r="43" spans="1:12" ht="10.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="48" t="s">
         <v>52</v>
       </c>
@@ -3105,7 +3105,7 @@
       <c r="J43" s="50"/>
       <c r="K43" s="50"/>
     </row>
-    <row r="44" spans="1:12" ht="10.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="48" t="s">
         <v>29</v>
       </c>
@@ -3121,43 +3121,38 @@
       <c r="K44" s="50"/>
     </row>
     <row r="45" spans="1:12" ht="10.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="71" t="s">
+      <c r="A45" s="136" t="s">
         <v>30</v>
       </c>
-      <c r="B45" s="71"/>
-      <c r="C45" s="71"/>
-      <c r="D45" s="71"/>
-      <c r="E45" s="71"/>
-      <c r="F45" s="71"/>
-      <c r="G45" s="71"/>
-      <c r="H45" s="71"/>
-      <c r="I45" s="71"/>
-      <c r="J45" s="71"/>
-      <c r="K45" s="71"/>
+      <c r="B45" s="136"/>
+      <c r="C45" s="136"/>
+      <c r="D45" s="136"/>
+      <c r="E45" s="136"/>
+      <c r="F45" s="136"/>
+      <c r="G45" s="136"/>
+      <c r="H45" s="136"/>
+      <c r="I45" s="136"/>
+      <c r="J45" s="136"/>
+      <c r="K45" s="136"/>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="D33:K33"/>
-    <mergeCell ref="H29:K29"/>
-    <mergeCell ref="H30:K30"/>
-    <mergeCell ref="A34:K34"/>
-    <mergeCell ref="A35:K35"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="D30:G30"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="A45:K45"/>
+    <mergeCell ref="E1:K1"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="H31:K31"/>
+    <mergeCell ref="H32:K32"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="G6:K6"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="G7:K7"/>
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="H11:I11"/>
     <mergeCell ref="A18:K18"/>
@@ -3174,22 +3169,27 @@
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="D21:E21"/>
-    <mergeCell ref="A45:K45"/>
-    <mergeCell ref="E1:K1"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="A15:I15"/>
-    <mergeCell ref="H31:K31"/>
-    <mergeCell ref="H32:K32"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="G6:K6"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A9:K9"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="G7:K7"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="D33:K33"/>
+    <mergeCell ref="H29:K29"/>
+    <mergeCell ref="H30:K30"/>
+    <mergeCell ref="A34:K34"/>
+    <mergeCell ref="A35:K35"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A29:C29"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.78740157480314965" right="0.82677165354330717" top="0.94488188976377963" bottom="1.0629921259842521" header="0.31496062992125984" footer="0.31496062992125984"/>
